--- a/SantanderCS/doc/lsj 피처 분석.xlsx
+++ b/SantanderCS/doc/lsj 피처 분석.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\big20\git\big20-ML-project2-team3\SantanderCS\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\big20\git\big20-ML-project2-team3\SantanderCS\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A28010C-0242-45CA-8103-FA3A3387B928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B1F3637-C3E8-4678-AAE7-468305D8928C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" activeTab="3" xr2:uid="{AD4817E5-F76A-4F89-867E-BD8F107C32DF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{AD4817E5-F76A-4F89-867E-BD8F107C32DF}"/>
   </bookViews>
   <sheets>
     <sheet name="EJM" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="503">
   <si>
     <t>ID</t>
   </si>
@@ -1509,12 +1509,124 @@
     <t>고객 관련 내부 코드/75152</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>zero_count_rate</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>100.00%</t>
+  </si>
+  <si>
+    <t>97.76%</t>
+  </si>
+  <si>
+    <t>99.47%</t>
+  </si>
+  <si>
+    <t>99.97%</t>
+  </si>
+  <si>
+    <t>99.94%</t>
+  </si>
+  <si>
+    <t>99.99%</t>
+  </si>
+  <si>
+    <t>99.73%</t>
+  </si>
+  <si>
+    <t>99.96%</t>
+  </si>
+  <si>
+    <t>99.89%</t>
+  </si>
+  <si>
+    <t>99.95%</t>
+  </si>
+  <si>
+    <t>93.34%</t>
+  </si>
+  <si>
+    <t>87.07%</t>
+  </si>
+  <si>
+    <t>91.91%</t>
+  </si>
+  <si>
+    <t>90.78%</t>
+  </si>
+  <si>
+    <t>90.31%</t>
+  </si>
+  <si>
+    <t>91.41%</t>
+  </si>
+  <si>
+    <t>98.86%</t>
+  </si>
+  <si>
+    <t>95.11%</t>
+  </si>
+  <si>
+    <t>79.64%</t>
+  </si>
+  <si>
+    <t>81.40%</t>
+  </si>
+  <si>
+    <t>89.39%</t>
+  </si>
+  <si>
+    <t>65.71%</t>
+  </si>
+  <si>
+    <t>85.20%</t>
+  </si>
+  <si>
+    <t>67.62%</t>
+  </si>
+  <si>
+    <t>27.03%</t>
+  </si>
+  <si>
+    <t>97.09%</t>
+  </si>
+  <si>
+    <t>95.42%</t>
+  </si>
+  <si>
+    <t>95.71%</t>
+  </si>
+  <si>
+    <t>99.29%</t>
+  </si>
+  <si>
+    <t>99.84%</t>
+  </si>
+  <si>
+    <t>13.37%</t>
+  </si>
+  <si>
+    <t>99.81%</t>
+  </si>
+  <si>
+    <t>86.92%</t>
+  </si>
+  <si>
+    <t>84.62%</t>
+  </si>
+  <si>
+    <t>99.61%</t>
+  </si>
+  <si>
+    <t>99.54%</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1554,6 +1666,20 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1569,12 +1695,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -1583,7 +1724,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1611,6 +1752,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1971,8 +2116,8 @@
         <v>376</v>
       </c>
       <c r="G2" s="1">
-        <f>SUM(D76,KJH!D76,LKJ!D76,LSJ!D76,YJH!D76)</f>
-        <v>49</v>
+        <f>SUM(D76,KJH!D76,LKJ!D76,LSJ!E76,YJH!D76)</f>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -1990,7 +2135,7 @@
       </c>
       <c r="B4" s="8"/>
       <c r="G4" s="1">
-        <f>COUNTA(E2:E75,KJH!E2:E75,LKJ!E2:E75,LSJ!E2:E75,YJH!E2:E75)</f>
+        <f>COUNTA(E2:E75,KJH!E2:E75,LKJ!E2:E75,LSJ!F2:F75,YJH!E2:E75)</f>
         <v>0</v>
       </c>
     </row>
@@ -3420,18 +3565,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A72F2C05-F367-4C39-8365-CA4F7D6FC375}">
-  <dimension ref="A1:I104"/>
+  <dimension ref="A1:J104"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.75" customWidth="1"/>
     <col min="2" max="2" width="14.5" customWidth="1"/>
-    <col min="3" max="3" width="42.625" customWidth="1"/>
-    <col min="4" max="4" width="14.625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="21.375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.625" customWidth="1"/>
+    <col min="3" max="3" width="47" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="47" customWidth="1"/>
+    <col min="5" max="5" width="14.625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="21.375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>371</v>
       </c>
@@ -3441,20 +3587,23 @@
       <c r="C1" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>380</v>
       </c>
@@ -3464,30 +3613,38 @@
       <c r="C2" t="s">
         <v>438</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="G2">
-        <f>COUNTIF(D:D,"Y")</f>
-        <v>48</v>
-      </c>
-      <c r="H2" s="5" t="s">
+      <c r="D2" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="E2" s="1" t="str">
+        <f>IF(VALUE(SUBSTITUTE(D2,"%",""))&gt;=99,"Y","N")</f>
+        <v>Y</v>
+      </c>
+      <c r="H2">
+        <f>COUNTIF(E:E,"Y")</f>
+        <v>49</v>
+      </c>
+      <c r="I2" s="5" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>221</v>
       </c>
       <c r="B3" s="8"/>
-      <c r="D3" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="H3" s="5" t="s">
+      <c r="D3" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="E3" s="1" t="str">
+        <f t="shared" ref="E3:E66" si="0">IF(VALUE(SUBSTITUTE(D3,"%",""))&gt;=99,"Y","N")</f>
+        <v>Y</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>222</v>
       </c>
@@ -3495,14 +3652,18 @@
       <c r="C4" t="s">
         <v>439</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="H4" s="5" t="s">
+      <c r="D4" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="E4" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+      <c r="I4" s="5" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>223</v>
       </c>
@@ -3510,11 +3671,18 @@
       <c r="C5" t="s">
         <v>440</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="D5" s="10" t="s">
+        <v>468</v>
+      </c>
+      <c r="E5" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>N</v>
+      </c>
+      <c r="I5" s="5" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>224</v>
       </c>
@@ -3522,14 +3690,18 @@
       <c r="C6" t="s">
         <v>441</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="H6" s="5" t="s">
+      <c r="D6" s="10" t="s">
+        <v>469</v>
+      </c>
+      <c r="E6" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+      <c r="I6" s="5" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>225</v>
       </c>
@@ -3537,14 +3709,18 @@
       <c r="C7" t="s">
         <v>437</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="H7" s="5" t="s">
+      <c r="D7" s="10" t="s">
+        <v>470</v>
+      </c>
+      <c r="E7" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+      <c r="I7" s="5" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>226</v>
       </c>
@@ -3552,14 +3728,18 @@
       <c r="C8" t="s">
         <v>411</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="H8" s="5" t="s">
+      <c r="D8" s="10" t="s">
+        <v>471</v>
+      </c>
+      <c r="E8" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+      <c r="I8" s="5" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>227</v>
       </c>
@@ -3567,14 +3747,18 @@
       <c r="C9" t="s">
         <v>395</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="H9" s="5" t="s">
+      <c r="D9" s="10" t="s">
+        <v>470</v>
+      </c>
+      <c r="E9" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+      <c r="I9" s="5" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>228</v>
       </c>
@@ -3582,14 +3766,18 @@
       <c r="C10" t="s">
         <v>396</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="H10" s="5" t="s">
+      <c r="D10" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="E10" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+      <c r="I10" s="5" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>229</v>
       </c>
@@ -3597,11 +3785,15 @@
       <c r="C11" t="s">
         <v>397</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D11" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="E11" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>230</v>
       </c>
@@ -3609,11 +3801,15 @@
       <c r="C12" t="s">
         <v>412</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D12" s="10" t="s">
+        <v>473</v>
+      </c>
+      <c r="E12" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>231</v>
       </c>
@@ -3621,15 +3817,19 @@
       <c r="C13" t="s">
         <v>413</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="I13">
+      <c r="D13" s="10" t="s">
+        <v>474</v>
+      </c>
+      <c r="E13" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+      <c r="J13">
         <f>COUNTA(A2:A75)</f>
         <v>74</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>232</v>
       </c>
@@ -3637,11 +3837,15 @@
       <c r="C14" t="s">
         <v>398</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D14" s="10" t="s">
+        <v>475</v>
+      </c>
+      <c r="E14" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>233</v>
       </c>
@@ -3649,11 +3853,15 @@
       <c r="C15" t="s">
         <v>384</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D15" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="E15" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>234</v>
       </c>
@@ -3661,11 +3869,15 @@
       <c r="C16" t="s">
         <v>399</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D16" s="10" t="s">
+        <v>476</v>
+      </c>
+      <c r="E16" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>235</v>
       </c>
@@ -3673,11 +3885,15 @@
       <c r="C17" t="s">
         <v>400</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D17" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="E17" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>236</v>
       </c>
@@ -3685,11 +3901,15 @@
       <c r="C18" t="s">
         <v>414</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D18" s="10" t="s">
+        <v>470</v>
+      </c>
+      <c r="E18" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>237</v>
       </c>
@@ -3697,11 +3917,15 @@
       <c r="C19" t="s">
         <v>384</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D19" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="E19" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>238</v>
       </c>
@@ -3709,11 +3933,15 @@
       <c r="C20" t="s">
         <v>401</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D20" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="E20" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>442</v>
       </c>
@@ -3721,8 +3949,15 @@
       <c r="C21" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D21" s="10" t="s">
+        <v>477</v>
+      </c>
+      <c r="E21" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>N</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>239</v>
       </c>
@@ -3730,8 +3965,15 @@
       <c r="C22" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D22" s="10" t="s">
+        <v>478</v>
+      </c>
+      <c r="E22" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>N</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>240</v>
       </c>
@@ -3739,11 +3981,15 @@
       <c r="C23" t="s">
         <v>415</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D23" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="E23" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>241</v>
       </c>
@@ -3751,11 +3997,15 @@
       <c r="C24" t="s">
         <v>404</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D24" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="E24" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>242</v>
       </c>
@@ -3763,11 +4013,15 @@
       <c r="C25" t="s">
         <v>384</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D25" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="E25" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>243</v>
       </c>
@@ -3775,11 +4029,15 @@
       <c r="C26" t="s">
         <v>416</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D26" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="E26" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>244</v>
       </c>
@@ -3787,11 +4045,15 @@
       <c r="C27" t="s">
         <v>417</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D27" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="E27" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>382</v>
       </c>
@@ -3799,12 +4061,16 @@
       <c r="C28" t="s">
         <v>405</v>
       </c>
-      <c r="D28" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="H28" s="7"/>
-    </row>
-    <row r="29" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D28" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="E28" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+      <c r="I28" s="7"/>
+    </row>
+    <row r="29" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>383</v>
       </c>
@@ -3812,14 +4078,18 @@
       <c r="C29" t="s">
         <v>384</v>
       </c>
-      <c r="D29" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="H29" s="6" t="s">
+      <c r="D29" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="E29" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+      <c r="I29" s="6" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>245</v>
       </c>
@@ -3827,11 +4097,15 @@
       <c r="C30" t="s">
         <v>406</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D30" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="E30" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>246</v>
       </c>
@@ -3839,12 +4113,16 @@
       <c r="C31" t="s">
         <v>407</v>
       </c>
-      <c r="D31" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="H31" s="7"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D31" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="E31" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+      <c r="I31" s="7"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>247</v>
       </c>
@@ -3852,12 +4130,16 @@
       <c r="C32" s="6" t="s">
         <v>418</v>
       </c>
-      <c r="D32" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="H32" s="6"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D32" s="10" t="s">
+        <v>471</v>
+      </c>
+      <c r="E32" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+      <c r="I32" s="6"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>248</v>
       </c>
@@ -3865,12 +4147,16 @@
       <c r="C33" t="s">
         <v>419</v>
       </c>
-      <c r="D33" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="H33" s="6"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D33" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="E33" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+      <c r="I33" s="6"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>249</v>
       </c>
@@ -3878,12 +4164,16 @@
       <c r="C34" t="s">
         <v>420</v>
       </c>
-      <c r="D34" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="H34" s="7"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D34" s="10" t="s">
+        <v>473</v>
+      </c>
+      <c r="E34" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+      <c r="I34" s="7"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>250</v>
       </c>
@@ -3891,9 +4181,16 @@
       <c r="C35" t="s">
         <v>421</v>
       </c>
-      <c r="H35" s="6"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D35" s="10" t="s">
+        <v>479</v>
+      </c>
+      <c r="E35" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>N</v>
+      </c>
+      <c r="I35" s="6"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>251</v>
       </c>
@@ -3901,9 +4198,16 @@
       <c r="C36" t="s">
         <v>422</v>
       </c>
-      <c r="H36" s="6"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D36" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="E36" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>N</v>
+      </c>
+      <c r="I36" s="6"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>252</v>
       </c>
@@ -3911,9 +4215,16 @@
       <c r="C37" t="s">
         <v>423</v>
       </c>
-      <c r="H37" s="7"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D37" s="10" t="s">
+        <v>481</v>
+      </c>
+      <c r="E37" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>N</v>
+      </c>
+      <c r="I37" s="7"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>253</v>
       </c>
@@ -3921,9 +4232,16 @@
       <c r="C38" t="s">
         <v>424</v>
       </c>
-      <c r="H38" s="6"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D38" s="10" t="s">
+        <v>482</v>
+      </c>
+      <c r="E38" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>N</v>
+      </c>
+      <c r="I38" s="6"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>254</v>
       </c>
@@ -3931,9 +4249,16 @@
       <c r="C39" t="s">
         <v>425</v>
       </c>
-      <c r="H39" s="6"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D39" s="10" t="s">
+        <v>477</v>
+      </c>
+      <c r="E39" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>N</v>
+      </c>
+      <c r="I39" s="6"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>255</v>
       </c>
@@ -3941,9 +4266,16 @@
       <c r="C40" t="s">
         <v>426</v>
       </c>
-      <c r="H40" s="7"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D40" s="10" t="s">
+        <v>478</v>
+      </c>
+      <c r="E40" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>N</v>
+      </c>
+      <c r="I40" s="7"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>256</v>
       </c>
@@ -3951,9 +4283,16 @@
       <c r="C41" t="s">
         <v>465</v>
       </c>
-      <c r="H41" s="6"/>
-    </row>
-    <row r="42" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D41" s="10" t="s">
+        <v>483</v>
+      </c>
+      <c r="E41" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>N</v>
+      </c>
+      <c r="I41" s="6"/>
+    </row>
+    <row r="42" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>257</v>
       </c>
@@ -3961,12 +4300,16 @@
       <c r="C42" t="s">
         <v>384</v>
       </c>
-      <c r="D42" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="H42" s="6"/>
-    </row>
-    <row r="43" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D42" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="E42" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+      <c r="I42" s="6"/>
+    </row>
+    <row r="43" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>258</v>
       </c>
@@ -3974,12 +4317,16 @@
       <c r="C43" t="s">
         <v>384</v>
       </c>
-      <c r="D43" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="H43" s="7"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D43" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="E43" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+      <c r="I43" s="7"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>259</v>
       </c>
@@ -3987,9 +4334,16 @@
       <c r="C44" t="s">
         <v>427</v>
       </c>
-      <c r="H44" s="6"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D44" s="10" t="s">
+        <v>468</v>
+      </c>
+      <c r="E44" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>N</v>
+      </c>
+      <c r="I44" s="6"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>260</v>
       </c>
@@ -3997,9 +4351,16 @@
       <c r="C45" t="s">
         <v>428</v>
       </c>
-      <c r="H45" s="6"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D45" s="10" t="s">
+        <v>469</v>
+      </c>
+      <c r="E45" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+      <c r="I45" s="6"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>261</v>
       </c>
@@ -4007,12 +4368,16 @@
       <c r="C46" t="s">
         <v>429</v>
       </c>
-      <c r="D46" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="H46" s="7"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D46" s="10" t="s">
+        <v>470</v>
+      </c>
+      <c r="E46" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+      <c r="I46" s="7"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>262</v>
       </c>
@@ -4020,12 +4385,16 @@
       <c r="C47" t="s">
         <v>430</v>
       </c>
-      <c r="D47" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="H47" s="6"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D47" s="10" t="s">
+        <v>471</v>
+      </c>
+      <c r="E47" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+      <c r="I47" s="6"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>263</v>
       </c>
@@ -4033,12 +4402,16 @@
       <c r="C48" t="s">
         <v>431</v>
       </c>
-      <c r="D48" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="H48" s="6"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D48" s="10" t="s">
+        <v>470</v>
+      </c>
+      <c r="E48" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+      <c r="I48" s="6"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>264</v>
       </c>
@@ -4046,12 +4419,16 @@
       <c r="C49" t="s">
         <v>432</v>
       </c>
-      <c r="D49" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="H49" s="7"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D49" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="E49" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+      <c r="I49" s="7"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>265</v>
       </c>
@@ -4059,12 +4436,16 @@
       <c r="C50" t="s">
         <v>433</v>
       </c>
-      <c r="D50" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="H50" s="6"/>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D50" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="E50" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+      <c r="I50" s="6"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>266</v>
       </c>
@@ -4072,12 +4453,16 @@
       <c r="C51" t="s">
         <v>434</v>
       </c>
-      <c r="D51" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="H51" s="6"/>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D51" s="10" t="s">
+        <v>473</v>
+      </c>
+      <c r="E51" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+      <c r="I51" s="6"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>267</v>
       </c>
@@ -4085,12 +4470,16 @@
       <c r="C52" t="s">
         <v>435</v>
       </c>
-      <c r="D52" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="H52" s="7"/>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D52" s="10" t="s">
+        <v>474</v>
+      </c>
+      <c r="E52" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+      <c r="I52" s="7"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>268</v>
       </c>
@@ -4098,12 +4487,16 @@
       <c r="C53" t="s">
         <v>436</v>
       </c>
-      <c r="D53" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="H53" s="6"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D53" s="10" t="s">
+        <v>475</v>
+      </c>
+      <c r="E53" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+      <c r="I53" s="6"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>269</v>
       </c>
@@ -4111,9 +4504,16 @@
       <c r="C54" t="s">
         <v>464</v>
       </c>
-      <c r="H54" s="6"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D54" s="10" t="s">
+        <v>484</v>
+      </c>
+      <c r="E54" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>N</v>
+      </c>
+      <c r="I54" s="6"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>270</v>
       </c>
@@ -4121,9 +4521,16 @@
       <c r="C55" t="s">
         <v>463</v>
       </c>
-      <c r="H55" s="7"/>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D55" s="10" t="s">
+        <v>485</v>
+      </c>
+      <c r="E55" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>N</v>
+      </c>
+      <c r="I55" s="7"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>271</v>
       </c>
@@ -4131,9 +4538,16 @@
       <c r="C56" t="s">
         <v>462</v>
       </c>
-      <c r="H56" s="6"/>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D56" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="E56" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>N</v>
+      </c>
+      <c r="I56" s="6"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>272</v>
       </c>
@@ -4141,9 +4555,16 @@
       <c r="C57" t="s">
         <v>461</v>
       </c>
-      <c r="H57" s="6"/>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D57" s="10" t="s">
+        <v>487</v>
+      </c>
+      <c r="E57" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>N</v>
+      </c>
+      <c r="I57" s="6"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>273</v>
       </c>
@@ -4151,9 +4572,16 @@
       <c r="C58" t="s">
         <v>460</v>
       </c>
-      <c r="H58" s="7"/>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D58" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="E58" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>N</v>
+      </c>
+      <c r="I58" s="7"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>274</v>
       </c>
@@ -4161,9 +4589,16 @@
       <c r="C59" t="s">
         <v>459</v>
       </c>
-      <c r="H59" s="6"/>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D59" s="10" t="s">
+        <v>489</v>
+      </c>
+      <c r="E59" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>N</v>
+      </c>
+      <c r="I59" s="6"/>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>275</v>
       </c>
@@ -4171,9 +4606,16 @@
       <c r="C60" t="s">
         <v>458</v>
       </c>
-      <c r="H60" s="6"/>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D60" s="10" t="s">
+        <v>490</v>
+      </c>
+      <c r="E60" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>N</v>
+      </c>
+      <c r="I60" s="6"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>276</v>
       </c>
@@ -4181,9 +4623,16 @@
       <c r="C61" t="s">
         <v>457</v>
       </c>
-      <c r="H61" s="7"/>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D61" s="10" t="s">
+        <v>491</v>
+      </c>
+      <c r="E61" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>N</v>
+      </c>
+      <c r="I61" s="7"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>277</v>
       </c>
@@ -4191,9 +4640,16 @@
       <c r="C62" t="s">
         <v>456</v>
       </c>
-      <c r="H62" s="6"/>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D62" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="E62" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>N</v>
+      </c>
+      <c r="I62" s="6"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>278</v>
       </c>
@@ -4201,9 +4657,16 @@
       <c r="C63" t="s">
         <v>455</v>
       </c>
-      <c r="H63" s="6"/>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D63" s="10" t="s">
+        <v>493</v>
+      </c>
+      <c r="E63" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>N</v>
+      </c>
+      <c r="I63" s="6"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>279</v>
       </c>
@@ -4211,9 +4674,16 @@
       <c r="C64" t="s">
         <v>454</v>
       </c>
-      <c r="H64" s="7"/>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D64" s="10" t="s">
+        <v>494</v>
+      </c>
+      <c r="E64" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>N</v>
+      </c>
+      <c r="I64" s="7"/>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>280</v>
       </c>
@@ -4221,12 +4691,16 @@
       <c r="C65" t="s">
         <v>453</v>
       </c>
-      <c r="D65" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="H65" s="6"/>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D65" s="10" t="s">
+        <v>495</v>
+      </c>
+      <c r="E65" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+      <c r="I65" s="6"/>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>281</v>
       </c>
@@ -4234,12 +4708,16 @@
       <c r="C66" t="s">
         <v>452</v>
       </c>
-      <c r="D66" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="H66" s="6"/>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D66" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="E66" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
+      </c>
+      <c r="I66" s="6"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>282</v>
       </c>
@@ -4247,12 +4725,16 @@
       <c r="C67" t="s">
         <v>451</v>
       </c>
-      <c r="D67" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="H67" s="7"/>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D67" s="10" t="s">
+        <v>496</v>
+      </c>
+      <c r="E67" s="1" t="str">
+        <f t="shared" ref="E67:E75" si="1">IF(VALUE(SUBSTITUTE(D67,"%",""))&gt;=99,"Y","N")</f>
+        <v>Y</v>
+      </c>
+      <c r="I67" s="7"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>283</v>
       </c>
@@ -4260,12 +4742,16 @@
       <c r="C68" t="s">
         <v>450</v>
       </c>
-      <c r="D68" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="H68" s="6"/>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D68" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="E68" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>Y</v>
+      </c>
+      <c r="I68" s="6"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>284</v>
       </c>
@@ -4273,12 +4759,16 @@
       <c r="C69" t="s">
         <v>449</v>
       </c>
-      <c r="D69" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="H69" s="6"/>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D69" s="10" t="s">
+        <v>471</v>
+      </c>
+      <c r="E69" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>Y</v>
+      </c>
+      <c r="I69" s="6"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>285</v>
       </c>
@@ -4286,9 +4776,16 @@
       <c r="C70" t="s">
         <v>448</v>
       </c>
-      <c r="H70" s="7"/>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D70" s="10" t="s">
+        <v>497</v>
+      </c>
+      <c r="E70" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>N</v>
+      </c>
+      <c r="I70" s="7"/>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>286</v>
       </c>
@@ -4296,12 +4793,16 @@
       <c r="C71" t="s">
         <v>447</v>
       </c>
-      <c r="D71" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="H71" s="6"/>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D71" s="10" t="s">
+        <v>498</v>
+      </c>
+      <c r="E71" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>Y</v>
+      </c>
+      <c r="I71" s="6"/>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>287</v>
       </c>
@@ -4309,9 +4810,16 @@
       <c r="C72" t="s">
         <v>446</v>
       </c>
-      <c r="H72" s="6"/>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D72" s="10" t="s">
+        <v>499</v>
+      </c>
+      <c r="E72" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>N</v>
+      </c>
+      <c r="I72" s="6"/>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>288</v>
       </c>
@@ -4319,9 +4827,16 @@
       <c r="C73" t="s">
         <v>445</v>
       </c>
-      <c r="H73" s="7"/>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D73" s="10" t="s">
+        <v>500</v>
+      </c>
+      <c r="E73" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>N</v>
+      </c>
+      <c r="I73" s="7"/>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>289</v>
       </c>
@@ -4329,12 +4844,16 @@
       <c r="C74" t="s">
         <v>444</v>
       </c>
-      <c r="D74" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="H74" s="6"/>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D74" s="10" t="s">
+        <v>501</v>
+      </c>
+      <c r="E74" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>Y</v>
+      </c>
+      <c r="I74" s="6"/>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>290</v>
       </c>
@@ -4342,70 +4861,74 @@
       <c r="C75" t="s">
         <v>443</v>
       </c>
-      <c r="D75" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="H75" s="6"/>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D76" s="1">
-        <f>COUNTIF(D2:D75,"=Y")</f>
-        <v>48</v>
-      </c>
-      <c r="H76" s="7"/>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="H77" s="6"/>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="H78" s="6"/>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="H79" s="7"/>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="H80" s="6"/>
-    </row>
-    <row r="81" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H81" s="6"/>
-    </row>
-    <row r="82" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H82" s="6"/>
-    </row>
-    <row r="83" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H83" s="6"/>
-    </row>
-    <row r="84" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H84" s="6"/>
-    </row>
-    <row r="85" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H85" s="6"/>
-    </row>
-    <row r="86" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H86" s="6"/>
-    </row>
-    <row r="97" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H97" s="7"/>
-    </row>
-    <row r="99" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H99" s="6"/>
-    </row>
-    <row r="100" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H100" s="7"/>
-    </row>
-    <row r="101" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H101" s="6" t="s">
+      <c r="D75" s="10" t="s">
+        <v>502</v>
+      </c>
+      <c r="E75" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>Y</v>
+      </c>
+      <c r="I75" s="6"/>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E76" s="1">
+        <f>COUNTIF(E2:E75,"=Y")</f>
+        <v>49</v>
+      </c>
+      <c r="I76" s="7"/>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I77" s="6"/>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I78" s="6"/>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I79" s="7"/>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I80" s="6"/>
+    </row>
+    <row r="81" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I81" s="6"/>
+    </row>
+    <row r="82" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I82" s="6"/>
+    </row>
+    <row r="83" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I83" s="6"/>
+    </row>
+    <row r="84" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I84" s="6"/>
+    </row>
+    <row r="85" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I85" s="6"/>
+    </row>
+    <row r="86" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I86" s="6"/>
+    </row>
+    <row r="97" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I97" s="7"/>
+    </row>
+    <row r="99" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I99" s="6"/>
+    </row>
+    <row r="100" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I100" s="7"/>
+    </row>
+    <row r="101" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I101" s="6" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="102" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H102" s="6"/>
-    </row>
-    <row r="103" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H103" s="7"/>
-    </row>
-    <row r="104" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H104" s="6" t="s">
+    <row r="102" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I102" s="6"/>
+    </row>
+    <row r="103" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I103" s="7"/>
+    </row>
+    <row r="104" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I104" s="6" t="s">
         <v>410</v>
       </c>
     </row>
